--- a/食品致病性微生物污染事件_语音文档.xlsx
+++ b/食品致病性微生物污染事件_语音文档.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\XWJ\GWA10343033_New\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16500" windowHeight="9390" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="知识宣教" sheetId="1" r:id="rId1"/>
@@ -53,7 +58,7 @@
     <t>张医生</t>
   </si>
   <si>
-    <t>您好，我是海河市中心医院急诊科张医生，前我院接诊了一批患者，均有不同程度的呕吐、腹痛、腹泻、发热，他们都是共同参加寿宴的家人，我怀疑是食源性疾病事件，特向贵单位报告。</t>
+    <t>您好，我是海河市中心医院急诊科张医生，目前我院接诊了一批患者，均有不同程度的呕吐、腹痛、腹泻、发热，他们都是共同参加寿宴的家人，我怀疑是食源性疾病事件，特向贵单位报告。</t>
   </si>
   <si>
     <t>旁白</t>
@@ -1891,8 +1896,7 @@
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="14" style="6"/>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="2" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="57.7416666666667" style="7" customWidth="1"/>
   </cols>
   <sheetData>
